--- a/data/templates/BCEndlineNgay (22)_Empty.xlsx
+++ b/data/templates/BCEndlineNgay (22)_Empty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leuti\Desktop\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A1F3DF-4757-44A8-B5C4-087A32205DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50EE84D-8147-44C7-AFAB-2E579EB7FD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t>Code:BM11/QT 13/CL01
 Revison:01
 Issued date:10/10/2024</t>
-  </si>
-  <si>
-    <t>Daisy</t>
   </si>
   <si>
     <t>Ngày
@@ -95,9 +92,6 @@
     <t>Tổng</t>
   </si>
   <si>
-    <t>LSX:... -- MH: ...</t>
-  </si>
-  <si>
     <r>
       <t>Mã Hàng/</t>
     </r>
@@ -122,15 +116,9 @@
       </rPr>
       <t>Style:</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>…</t>
-    </r>
+  </si>
+  <si>
+    <t>LSX:752 -- MH: 0088 342 29 V0.3</t>
   </si>
   <si>
     <r>
@@ -157,15 +145,9 @@
       </rPr>
       <t>Line:</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>…</t>
-    </r>
+  </si>
+  <si>
+    <t>Daisy</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1311,7 @@
     <col min="3" max="3" width="30.75" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="31.125" style="1" customWidth="1"/>
@@ -1413,16 +1395,16 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="I5" s="4"/>
       <c r="K5" s="4"/>
@@ -1433,28 +1415,28 @@
     </row>
     <row r="7" spans="1:21" ht="33.6" customHeight="1">
       <c r="A7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>4</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>5</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
@@ -1463,52 +1445,52 @@
     <row r="8" spans="1:21" ht="35.25" customHeight="1">
       <c r="A8" s="14"/>
       <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="F8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="J8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="N8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="P8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1518,40 +1500,40 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1561,40 +1543,40 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1604,40 +1586,40 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1647,40 +1629,40 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1690,40 +1672,40 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1733,45 +1715,45 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6">
         <f>SUM(B9:B14)</f>
@@ -1786,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="6">
         <f>SUM(F9:F14)</f>
@@ -1801,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="6">
         <f>SUM(J9:J14)</f>
@@ -1816,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N15" s="6">
         <f>SUM(N9:N14)</f>
@@ -1831,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
